--- a/resource/groundTruths/decision/CF_M09_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M09_ground_truth_decision.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23343770-FAE8-D74D-8885-0FDFBA561240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83110145-BAF8-C346-A16A-C7AC3D929DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14760" yWindow="920" windowWidth="14480" windowHeight="16560" xr2:uid="{AD170A51-FACD-004C-B77E-B4AACF24B987}"/>
   </bookViews>
@@ -58,30 +58,6 @@
     <t>CF_M09</t>
   </si>
   <si>
-    <t>CF_M09_AD1</t>
-  </si>
-  <si>
-    <t>CF_M09_AD2</t>
-  </si>
-  <si>
-    <t>CF_M09_AD3</t>
-  </si>
-  <si>
-    <t>CF_M09_AD4</t>
-  </si>
-  <si>
-    <t>CF_M09_AD5</t>
-  </si>
-  <si>
-    <t>CF_M09_AD6</t>
-  </si>
-  <si>
-    <t>CF_M09_AD7</t>
-  </si>
-  <si>
-    <t>CF_M09_AD8</t>
-  </si>
-  <si>
     <t>To decouple the components of the client-server model, a three-tier architecture has been used.</t>
   </si>
   <si>
@@ -127,25 +103,49 @@
     <t>It has been used to deploy the web application and the REST API. AWS was chosen over other alternatives such as Google Cloud [43] or Microsoft Azure [44] due to its popularity and low cost.</t>
   </si>
   <si>
-    <t>CF_M09_C10</t>
-  </si>
-  <si>
-    <t>CF_M09_C11</t>
-  </si>
-  <si>
-    <t>CF_M09_C12, CF_M09_C13</t>
-  </si>
-  <si>
-    <t>CF_M09_C13</t>
-  </si>
-  <si>
-    <t>CF_M09_C14</t>
-  </si>
-  <si>
-    <t>CF_M09_C14, CF_M09_C15</t>
-  </si>
-  <si>
-    <t>CF_M09_C15, CF_M09_C16</t>
+    <t>*CF_M09_C10</t>
+  </si>
+  <si>
+    <t>*CF_M09_C11</t>
+  </si>
+  <si>
+    <t>*CF_M09_C12, *CF_M09_C13</t>
+  </si>
+  <si>
+    <t>*CF_M09_C14, *CF_M09_C15</t>
+  </si>
+  <si>
+    <t>*CF_M09_C13</t>
+  </si>
+  <si>
+    <t>*CF_M09_C14</t>
+  </si>
+  <si>
+    <t>*CF_M09_C15, *CF_M09_C16</t>
+  </si>
+  <si>
+    <t>CF_M09_AD01</t>
+  </si>
+  <si>
+    <t>CF_M09_AD02</t>
+  </si>
+  <si>
+    <t>CF_M09_AD03</t>
+  </si>
+  <si>
+    <t>CF_M09_AD04</t>
+  </si>
+  <si>
+    <t>CF_M09_AD05</t>
+  </si>
+  <si>
+    <t>CF_M09_AD06</t>
+  </si>
+  <si>
+    <t>CF_M09_AD07</t>
+  </si>
+  <si>
+    <t>CF_M09_AD08</t>
   </si>
 </sst>
 </file>
@@ -556,16 +556,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
       </c>
       <c r="F2">
         <v>55</v>
@@ -576,16 +576,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>57</v>
@@ -596,16 +596,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>58</v>
@@ -616,16 +616,16 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F5">
         <v>60</v>
@@ -636,16 +636,16 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>60</v>
@@ -656,16 +656,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>60</v>
@@ -676,16 +676,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F8">
         <v>60</v>
@@ -696,16 +696,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F9">
         <v>61</v>

--- a/resource/groundTruths/decision/CF_M09_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M09_ground_truth_decision.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83110145-BAF8-C346-A16A-C7AC3D929DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEAC30D8-A84F-804C-A5EB-FF851C6FF8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14760" yWindow="920" windowWidth="14480" windowHeight="16560" xr2:uid="{AD170A51-FACD-004C-B77E-B4AACF24B987}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>Document ID</t>
   </si>
@@ -46,9 +46,6 @@
     <t>AD ID</t>
   </si>
   <si>
-    <t>Architectural Element</t>
-  </si>
-  <si>
     <t>AD Source</t>
   </si>
   <si>
@@ -146,6 +143,33 @@
   </si>
   <si>
     <t>CF_M09_AD08</t>
+  </si>
+  <si>
+    <t>Architectural Element ID</t>
+  </si>
+  <si>
+    <t>CF_M09_AD09</t>
+  </si>
+  <si>
+    <t>CF_M09_AD10</t>
+  </si>
+  <si>
+    <t>Both the business layer and the data layer are divided into different services (each running on different machines) to improve the security, scalability, and availability of the system.</t>
+  </si>
+  <si>
+    <t>CF_M09_C05, *CF_M09_C12, *CF_M09_C17</t>
+  </si>
+  <si>
+    <t>CF_M09_AU09, CF_M09_AU10</t>
+  </si>
+  <si>
+    <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB, which the business service has access to.</t>
+  </si>
+  <si>
+    <t>CF_M09_AU26</t>
+  </si>
+  <si>
+    <t>CF_M09_C04</t>
   </si>
 </sst>
 </file>
@@ -528,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005C0D04-1682-5647-8BDC-78F769BDB3A7}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -539,13 +563,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>1</v>
@@ -553,19 +577,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
       <c r="F2">
         <v>55</v>
@@ -573,19 +597,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>57</v>
@@ -593,19 +617,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
         <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
       </c>
       <c r="F4">
         <v>58</v>
@@ -613,19 +637,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5">
         <v>60</v>
@@ -633,19 +657,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <v>60</v>
@@ -653,19 +677,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>60</v>
@@ -673,19 +697,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8">
         <v>60</v>
@@ -693,22 +717,62 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
